--- a/src/template/tabela_indice_R.xlsx
+++ b/src/template/tabela_indice_R.xlsx
@@ -1,54 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_E965DBE7025B00CEE007E0154AB5463FB463B02F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B40C1F-5924-4100-BC0E-FD3BF741F829}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice R" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="indice_R" sheetId="1" r:id="rId1"/>
+    <sheet name="base" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Tabela de Pontuação das Atividades do Grupo de Pesquisa (Índice R)</t>
+  </si>
+  <si>
+    <t>Nome do Grupo:</t>
+  </si>
+  <si>
+    <t>Número de Componentes do Grupo:</t>
+  </si>
+  <si>
+    <t>Atividade</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Pontos</t>
+  </si>
+  <si>
+    <t>Sub-Total</t>
+  </si>
+  <si>
+    <t>Periódicos Indexados</t>
+  </si>
+  <si>
+    <t>Periódicos não indexados constantes na base Qualis</t>
+  </si>
+  <si>
+    <t>Anais de Congressos</t>
+  </si>
+  <si>
+    <t>Livros - Completo</t>
+  </si>
+  <si>
+    <t>Livros - Organizado</t>
+  </si>
+  <si>
+    <t>Livros - Capítulo</t>
+  </si>
+  <si>
+    <t>Livros - Tradução</t>
+  </si>
+  <si>
+    <t>Projeto de Pesquisa - Coordenador</t>
+  </si>
+  <si>
+    <t>Projeto de Pesquisa - Participação</t>
+  </si>
+  <si>
+    <t>Bolsa de Produtividade PQ ou DT</t>
+  </si>
+  <si>
+    <t>Carta Patente</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF99"/>
+        <fgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,109 +141,59 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -451,277 +481,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="52.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tabela de Pontuação das Atividades do Grupo de Pesquisa (Índice R)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Nome do Grupo:</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Número de Componentes do Grupo:</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Atividade</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Unidade</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Quantidade</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Pontos</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Sub-Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PESQUISA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Periódicos Indexados</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>total de trabalhos publicados (últimos 3 anos)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="4" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <f>COUNTIF(base!$C:$C,A4)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Periódicos não indexados constantes na base Qualis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="n">
+      <c r="D4" s="4">
+        <f>B4*C4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <f>COUNTIF(base!$C:$C,A5)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Anais de Congressos</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="4" t="n">
+      <c r="D5" s="4">
+        <f t="shared" ref="D5:D14" si="0">B5*C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <f>COUNTIF(base!$C:$C,A6)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Livros - Completo</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="4" t="n">
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2">
+        <f>COUNTIF(base!$C:$C,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Livros - Organizado</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="4" t="n">
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <f>COUNTIF(base!$C:$C,A8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Livros - Capítulo</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="4" t="n">
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2">
+        <f>COUNTIF(base!$C:$C,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Livros - Tradução</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="4" t="n">
+      <c r="D9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <f>COUNTIF(base!$C:$C,A10)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Projeto de Pesquisa - Coordenador</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>total de projetos aprovados (últimos 3 anos)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="4" t="n">
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <f>COUNTIF(base!$C:$C,A11)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Projeto de Pesquisa - Participação</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="4" t="n">
+      <c r="D11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <f>COUNTIF(base!$C:$C,A12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Bolsa de Produtividade PQ ou DT</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="4" t="n">
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2">
+        <f>COUNTIF(base!$C:$C,A13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Carta Patente</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>total de Cartas Patentes registradas (últimos 3 anos)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="4" t="n">
+      <c r="D13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2">
+        <f>COUNTIF(base!$C:$C,A14)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5">
+        <f>SUM(D4:D14)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6AAE870-AF56-4CB7-B6BF-D4A557769D57}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>